--- a/Result/profitability/2491.xlsx
+++ b/Result/profitability/2491.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0.165</v>
+        <v>3.9075</v>
       </c>
       <c r="N2" t="n">
-        <v>27.40875</v>
+        <v>27.70625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.07</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13375</v>
+        <v>3.746250000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>22.99625</v>
+        <v>16.46375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08</v>
+        <v>3.865</v>
       </c>
       <c r="N4" t="n">
-        <v>11.05625</v>
+        <v>12.815</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.63</v>
       </c>
       <c r="M5" t="n">
-        <v>0.14625</v>
+        <v>3.715</v>
       </c>
       <c r="N5" t="n">
-        <v>8.98</v>
+        <v>9.17</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02500000000000001</v>
+        <v>3.53125</v>
       </c>
       <c r="N6" t="n">
-        <v>5.288749999999999</v>
+        <v>5.627499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.26</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.14125</v>
+        <v>3.381250000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>2.203749999999999</v>
+        <v>0.07499999999999829</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.7</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.34625</v>
+        <v>3.1875</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.016250000000001</v>
+        <v>-1.575000000000002</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-3.43</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8812500000000001</v>
+        <v>-0.88125</v>
       </c>
       <c r="N9" t="n">
         <v>-5.491250000000001</v>
@@ -1772,10 +1772,10 @@
         <v>-0.55</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8600000000000001</v>
+        <v>-0.86</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.496250000000002</v>
+        <v>-5.496250000000003</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
         <v>8.210000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1925</v>
+        <v>0.1925000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.633750000000001</v>
+        <v>-3.633750000000002</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>46</v>
+      </c>
+      <c r="D75" t="n">
+        <v>34</v>
+      </c>
+      <c r="E75" t="n">
+        <v>12</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-93</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-204.35%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3144</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3051</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2388</v>
+      </c>
+      <c r="L75" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.84875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.025</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="X75" t="n">
+        <v>33.25882352941176</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.7759084791386273</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>50.08771929824562</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.0611178126256533</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
